--- a/runs/RELX/2026-10-14/bear/scratch/g_beta_5yw/out/dcf.xlsx
+++ b/runs/RELX/2026-10-14/bear/scratch/g_beta_5yw/out/dcf.xlsx
@@ -599,7 +599,7 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>0.05</v>
+        <v>0.042</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         <v/>
       </c>
       <c r="I15" s="4" t="n">
-        <v>2163.434104650448</v>
+        <v>2205.332986867939</v>
       </c>
     </row>
     <row r="16">
@@ -1392,7 +1392,7 @@
         <v/>
       </c>
       <c r="C17" s="6" t="n">
-        <v>0.087505</v>
+        <v>0.0822242</v>
       </c>
     </row>
     <row r="18">
@@ -1420,7 +1420,7 @@
         <v/>
       </c>
       <c r="C19" s="6" t="n">
-        <v>0.08237433914</v>
+        <v>0.077770432084</v>
       </c>
     </row>
     <row r="20">
@@ -1434,7 +1434,7 @@
         <v/>
       </c>
       <c r="C20" s="4" t="n">
-        <v>11477.8395591746</v>
+        <v>11598.24322946429</v>
       </c>
     </row>
     <row r="21">
@@ -1462,7 +1462,7 @@
         <v/>
       </c>
       <c r="C22" s="4" t="n">
-        <v>46161.1547949493</v>
+        <v>49839.88210591285</v>
       </c>
     </row>
     <row r="23">
@@ -1476,7 +1476,7 @@
         <v/>
       </c>
       <c r="C23" s="4" t="n">
-        <v>32327.93551663924</v>
+        <v>35580.23519445985</v>
       </c>
     </row>
     <row r="24">
@@ -1490,7 +1490,7 @@
         <v/>
       </c>
       <c r="C24" s="4" t="n">
-        <v>43805.77507581384</v>
+        <v>47178.47842392413</v>
       </c>
     </row>
     <row r="25">
@@ -1518,7 +1518,7 @@
         <v/>
       </c>
       <c r="C26" s="4" t="n">
-        <v>36808.77507581384</v>
+        <v>40181.47842392413</v>
       </c>
     </row>
     <row r="27">
@@ -1532,7 +1532,7 @@
         <v/>
       </c>
       <c r="C27" s="4" t="n">
-        <v>36036.2932430065</v>
+        <v>39474.7732981599</v>
       </c>
     </row>
     <row r="28">
@@ -1546,7 +1546,7 @@
         <v/>
       </c>
       <c r="C28" s="4" t="n">
-        <v>20.66591859796949</v>
+        <v>22.63780145621357</v>
       </c>
     </row>
     <row r="29">
@@ -1560,7 +1560,7 @@
         <v/>
       </c>
       <c r="C29" s="4" t="n">
-        <v>2066.591859796948</v>
+        <v>2263.780145621357</v>
       </c>
     </row>
     <row r="30">
@@ -1574,7 +1574,7 @@
         <v/>
       </c>
       <c r="C30" s="6" t="n">
-        <v>-0.254207196</v>
+        <v>-0.1830457793</v>
       </c>
     </row>
   </sheetData>
